--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833902</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833920</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833922</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833918</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833923</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833904</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833900</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833926</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833927</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833928</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833929</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833894</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833896</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2437,6 +2517,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833897</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2557,6 +2642,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833903</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2677,6 +2767,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833910</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2797,6 +2892,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833915</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2917,6 +3017,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833917</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3037,6 +3142,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833919</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3157,6 +3267,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833932</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3277,6 +3392,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833933</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3397,6 +3517,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833934</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3509,6 +3634,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833893</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3616,6 +3746,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833901</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3723,6 +3858,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833906</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3830,6 +3970,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833921</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3942,6 +4087,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833895</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4049,6 +4199,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833905</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4156,6 +4311,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833907</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4263,6 +4423,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833911</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4370,6 +4535,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833912</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4482,6 +4652,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833913</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4589,6 +4764,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833914</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4696,6 +4876,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833916</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4803,6 +4988,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833925</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4910,6 +5100,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833924</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5017,8 +5212,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134833931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>134833927</v>
       </c>
       <c r="B10" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>134833928</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>134833929</v>
       </c>
       <c r="B12" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>134833930</v>
       </c>
       <c r="B13" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>134833892</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>134833894</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>134833896</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>134833897</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>134833903</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>134833910</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>134833915</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>134833917</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>134833919</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>134833932</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>134833933</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>134833934</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>134833927</v>
       </c>
       <c r="B10" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>134833928</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>134833929</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>134833930</v>
       </c>
       <c r="B13" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>134833927</v>
       </c>
       <c r="B10" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>134833928</v>
       </c>
       <c r="B11" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>134833929</v>
       </c>
       <c r="B12" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>134833930</v>
       </c>
       <c r="B13" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>134833892</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>134833894</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>134833896</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>134833897</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>134833903</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>134833910</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>134833915</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>134833917</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>134833919</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>134833932</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>134833933</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>134833934</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>134833927</v>
       </c>
       <c r="B10" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>134833928</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>134833929</v>
       </c>
       <c r="B12" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>134833930</v>
       </c>
       <c r="B13" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>134833892</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>134833894</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>134833896</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>134833897</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>134833903</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>134833910</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>134833915</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>134833917</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>134833919</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>134833932</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>134833933</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>134833934</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 28751-2026 artfynd.xlsx
+++ b/artfynd/A 28751-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134833902</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134833920</v>
       </c>
       <c r="B3" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134833922</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134833918</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134833923</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134833904</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>134833900</v>
       </c>
       <c r="B8" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>134833926</v>
       </c>
       <c r="B9" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>134833927</v>
       </c>
       <c r="B10" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>134833928</v>
       </c>
       <c r="B11" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>134833929</v>
       </c>
       <c r="B12" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>134833930</v>
       </c>
       <c r="B13" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>134833892</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>134833894</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>134833896</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>134833897</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>134833903</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>134833910</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>134833915</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>134833917</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>134833919</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>134833932</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>134833933</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>134833934</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>134833893</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>134833901</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>134833906</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>134833921</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>134833895</v>
       </c>
       <c r="B30" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>134833905</v>
       </c>
       <c r="B31" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>134833907</v>
       </c>
       <c r="B32" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>134833911</v>
       </c>
       <c r="B33" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>134833912</v>
       </c>
       <c r="B34" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>134833913</v>
       </c>
       <c r="B35" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>134833914</v>
       </c>
       <c r="B36" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>134833916</v>
       </c>
       <c r="B37" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>134833925</v>
       </c>
       <c r="B38" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>134833924</v>
       </c>
       <c r="B39" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>134833931</v>
       </c>
       <c r="B40" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
